--- a/bd/pedidos.xlsx
+++ b/bd/pedidos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,26 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>julio@gmail.com</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-02-06 16:52:09</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>enviado</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bd/pedidos.xlsx
+++ b/bd/pedidos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,26 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>julio@gmail.com</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-02-06 16:52:09</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>enviado</t>
         </is>
       </c>
     </row>

--- a/bd/pedidos.xlsx
+++ b/bd/pedidos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>entregado</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nico@gmail.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03-03 16:58:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>enviado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nico@gmail.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03-03 20:05:49</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>

--- a/bd/pedidos.xlsx
+++ b/bd/pedidos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,170 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>nico@gmail.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:33:02</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:42:40</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:48:18</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:49:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-03-04 19:55:08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:02:08</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:02:37</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:05:34</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-03-04 20:06:17</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bd/pedidos.xlsx
+++ b/bd/pedidos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,6 +662,24 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-03-06 14:02:06</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
